--- a/output/pdf_financials_xlsx/PLXX.P.xlsx
+++ b/output/pdf_financials_xlsx/PLXX.P.xlsx
@@ -2525,16 +2525,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.046885</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.047448</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.036896</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.036896</v>
       </c>
     </row>
     <row r="93">
@@ -3819,7 +3819,11 @@
           <t>Share based payments reserve (note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PLXX.P.xlsx
+++ b/output/pdf_financials_xlsx/PLXX.P.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002158</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005408</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.00512</v>
       </c>
     </row>
     <row r="13">
@@ -1033,13 +1033,13 @@
         <v>-0.060577</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.022557</v>
+        <v>-0.024715</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.022815</v>
+        <v>-0.028223</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.03528</v>
+        <v>-0.0404</v>
       </c>
     </row>
     <row r="28">
@@ -1077,13 +1077,13 @@
         <v>-0.060577</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.022557</v>
+        <v>-0.024715</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.022815</v>
+        <v>-0.028223</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.03528</v>
+        <v>-0.0404</v>
       </c>
     </row>
     <row r="30">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.091957</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.177776</v>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.091957</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.177776</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">

--- a/output/pdf_financials_xlsx/PLXX.P.xlsx
+++ b/output/pdf_financials_xlsx/PLXX.P.xlsx
@@ -5382,7 +5382,11 @@
           <t>Issuance of common shares in private placement</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.105</v>
       </c>
